--- a/docs/harness/wirelist/ECU-cabin-pinouts.xlsx
+++ b/docs/harness/wirelist/ECU-cabin-pinouts.xlsx
@@ -11,11 +11,13 @@
     <sheet name="BULKHEAD (bh_fw)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="FRONT WS INLINE (ix_ws_front_p)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="PEDAL (aps)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="+5V BUS (bus_5v_bha_p)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="SENSOR GND BUS (bus_gnd_bha_p)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ECU-B (Link G4X plug B, centre " sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="IX-FUEL inline to fuel sender l" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="IX-WS-R inline to rear VRC (das" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="ECU-B (Link G4X plug B, centre " sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="IX-FUEL inline to fuel sender l" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="IX-WS-R inline to rear VRC (das" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="BUS-5V (bus_5v_p)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="BUS-5V-2 (bus_5v2_p)" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="BUS-GNDOUT-A (bus_gnd_a_p)" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="BUS-GNDOUT-B (bus_gnd_b_p)" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ECU-A (ecu_a)'!$A$2:$D$36</definedName>
@@ -26,16 +28,20 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'FRONT WS INLINE (ix_ws_front_p)'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'PEDAL (aps)'!$A$2:$D$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'PEDAL (aps)'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'+5V BUS (bus_5v_bha_p)'!$A$2:$D$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'+5V BUS (bus_5v_bha_p)'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'SENSOR GND BUS (bus_gnd_bha_p)'!$A$2:$D$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'SENSOR GND BUS (bus_gnd_bha_p)'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'ECU-B (Link G4X plug B, centre '!$A$2:$D$36</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'ECU-B (Link G4X plug B, centre '!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'IX-FUEL inline to fuel sender l'!$A$2:$D$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'IX-FUEL inline to fuel sender l'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'IX-WS-R inline to rear VRC (das'!$A$2:$D$8</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'IX-WS-R inline to rear VRC (das'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ECU-B (Link G4X plug B, centre '!$A$2:$D$36</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'ECU-B (Link G4X plug B, centre '!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'IX-FUEL inline to fuel sender l'!$A$2:$D$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'IX-FUEL inline to fuel sender l'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'IX-WS-R inline to rear VRC (das'!$A$2:$D$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'IX-WS-R inline to rear VRC (das'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'BUS-5V (bus_5v_p)'!$A$2:$D$14</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'BUS-5V (bus_5v_p)'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'BUS-5V-2 (bus_5v2_p)'!$A$2:$D$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'BUS-5V-2 (bus_5v2_p)'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'BUS-GNDOUT-A (bus_gnd_a_p)'!$A$2:$D$14</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'BUS-GNDOUT-A (bus_gnd_a_p)'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'BUS-GNDOUT-B (bus_gnd_b_p)'!$A$2:$D$14</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'BUS-GNDOUT-B (bus_gnd_b_p)'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1097,7 +1103,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>splice sp_gndout (SP-GNDOUT-A: sensor ground)</t>
+          <t>BUS-GNDOUT-A pin 1</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1125,7 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>splice sp_chassis (SP-GND-CHASSIS: ECU power ground)</t>
+          <t>splice sp_gnd_ecu (SP-GND-ECU: ECU power ground)</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1279,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>splice sp_5v (SP-5V-A: +5 V sensor supply)</t>
+          <t>BUS-5V pin 1</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1323,538 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>splice sp_chassis (SP-GND-CHASSIS: ECU power ground)</t>
+          <t>splice sp_gnd_ecu (SP-GND-ECU: ECU power ground)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:D36"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BUS-GNDOUT-A (bus_gnd_a_p)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Pin</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Wire</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Other end</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>w68</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Sensor gnd from A24</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>ECU-A pin A24</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>w_rail_sp_gndout_c</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Gnd IAT/TPS/coolant</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>BULKHEAD pin 34</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>w_gnd_a_c41</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Gnd crank sensor</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>BULKHEAD pin 75</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>w_gnd_a_c42</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Gnd cam sensor</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>BULKHEAD pin 65</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>w_gnd_a_c43</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Gnd turbo speed</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>BULKHEAD pin 56</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>w_gnd_a_c44</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Gnd flex + MAP</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>BULKHEAD pin 18</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>w40</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Pedal 1 ground</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>PEDAL pin 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>w_aps_gnd2</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Pedal 2 ground</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>PEDAL pin 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>cab_fspur_gnd</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Front VRC ground</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>FRONT WS INLINE pin 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr"/>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:D14"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BUS-GNDOUT-B (bus_gnd_b_p)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Pin</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Wire</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Other end</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>w69</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Sensor gnd from B22</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>ECU-B (Link G4X plug B, centre dash) pin B22</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>w45</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Fuel level ground</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>IX-FUEL inline to fuel sender lead (trunk end) pin 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>cab_rspur_gnd</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Rear VRC ground</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>IX-WS-R inline to rear VRC (dash above ECU) pin 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>w_ac_btn_gnd</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>A/C btn divider gnd</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>3.9k A/C switch divider, bottom pin 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>w_evap_rtn</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Evap thermistor gnd</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>OEM evaporator thermistor A24 pin 2, at the evap case</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>w12_c</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Knock sensor (-)</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>BULKHEAD pin 72</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>w_gnd_b_c19</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Gnd oil/clnt/temps</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>BULKHEAD pin 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>w_gnd_b_c21</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Gnd fuel press + VSS</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>BULKHEAD pin 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr"/>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:D14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -1580,7 +2112,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>+5V BUS pin 6</t>
+          <t>BUS-5V pin 6</t>
         </is>
       </c>
     </row>
@@ -1620,7 +2152,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>splice sp_gnd_bhb (SP-GND-BHB)</t>
+          <t>BUS-GNDOUT-B pin 8</t>
         </is>
       </c>
     </row>
@@ -1640,7 +2172,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>+5V BUS pin 3</t>
+          <t>BUS-5V pin 3</t>
         </is>
       </c>
     </row>
@@ -1680,7 +2212,7 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>SENSOR GND BUS pin 6</t>
+          <t>BUS-GNDOUT-A pin 6</t>
         </is>
       </c>
     </row>
@@ -1804,7 +2336,7 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>+5V BUS pin 7</t>
+          <t>BUS-5V pin 7</t>
         </is>
       </c>
     </row>
@@ -1844,7 +2376,7 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>+5V BUS pin 5</t>
+          <t>BUS-5V pin 5</t>
         </is>
       </c>
     </row>
@@ -1884,7 +2416,7 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>splice sp_gnd_bhb (SP-GND-BHB)</t>
+          <t>BUS-GNDOUT-B pin 7</t>
         </is>
       </c>
     </row>
@@ -1984,7 +2516,7 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>SENSOR GND BUS pin 2</t>
+          <t>BUS-GNDOUT-A pin 2</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2608,7 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>+5V BUS pin 2</t>
+          <t>BUS-5V pin 2</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2796,7 @@
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>+5V BUS pin 4</t>
+          <t>BUS-5V pin 4</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2860,7 @@
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>SENSOR GND BUS pin 5</t>
+          <t>BUS-GNDOUT-A pin 5</t>
         </is>
       </c>
     </row>
@@ -2492,7 +3024,7 @@
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>SENSOR GND BUS pin 4</t>
+          <t>BUS-GNDOUT-A pin 4</t>
         </is>
       </c>
     </row>
@@ -2632,7 +3164,7 @@
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>splice sp_gnd_bhb (SP-GND-BHB)</t>
+          <t>BUS-GNDOUT-B pin 6</t>
         </is>
       </c>
     </row>
@@ -2692,7 +3224,7 @@
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>SENSOR GND BUS pin 3</t>
+          <t>BUS-GNDOUT-A pin 3</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3564,7 @@
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>splice sp_chassis (SP-GND-CHASSIS: ECU power ground)</t>
+          <t>POWER box NEG bar M8 stud (glove box)</t>
         </is>
       </c>
     </row>
@@ -3175,7 +3707,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>splice sp_5v (SP-5V-A: +5 V sensor supply)</t>
+          <t>BUS-5V pin 10</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3727,7 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>splice sp_gndout (SP-GNDOUT-A: sensor ground)</t>
+          <t>BUS-GNDOUT-A pin 9</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3870,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>splice sp_5v_2 (SP-5V-PEDAL: +5 V to pedal + cruise)</t>
+          <t>BUS-5V pin 9</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3890,7 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>splice sp_gndout (SP-GNDOUT-A: sensor ground)</t>
+          <t>BUS-GNDOUT-A pin 8</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3930,7 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>splice sp_5v_2 (SP-5V-PEDAL: +5 V to pedal + cruise)</t>
+          <t>BUS-5V pin 8</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3950,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>splice sp_gndout (SP-GNDOUT-A: sensor ground)</t>
+          <t>BUS-GNDOUT-A pin 7</t>
         </is>
       </c>
     </row>
@@ -3450,404 +3982,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>+5V BUS (bus_5v_bha_p)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Pin</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Wire</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Other end</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>w_5v_bha_trunk</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>+5 V sensor supply</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>splice sp_5v (SP-5V-A: +5 V sensor supply)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>w_rail_sp_5v_c</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>+5 V throttle sensor</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>BULKHEAD pin 41</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>w_5v_a_c39</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>+5 V MAP sensor</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>BULKHEAD pin 16</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>w_5v_a_c40</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>+5 V turbo speed</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>BULKHEAD pin 52</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>w_5v_brail_c45</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>+5 V oil pressure</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>BULKHEAD pin 27</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>w_5v_brail_c46</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>+5 V fuel pressure</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>BULKHEAD pin 13</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>w_5v_brail_c47</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>+5 V coolant press</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>BULKHEAD pin 25</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr"/>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A2:D10"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>SENSOR GND BUS (bus_gnd_bha_p)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Pin</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Wire</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Other end</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>w_gnd_bha_trunk</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Sensor ground</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>splice sp_gndout (SP-GNDOUT-A: sensor ground)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>w_rail_sp_gndout_c</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>Gnd IAT/TPS/coolant</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>BULKHEAD pin 34</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>w_gnd_a_c41</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Gnd crank sensor</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>BULKHEAD pin 75</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>w_gnd_a_c42</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Gnd cam sensor</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>BULKHEAD pin 65</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>w_gnd_a_c43</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Gnd turbo speed</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>BULKHEAD pin 56</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>w_gnd_a_c44</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Gnd flex + MAP</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>BULKHEAD pin 18</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr"/>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A2:D10"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4315,7 +4449,7 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>splice sp_gndout_b (SP-GNDOUT-B)</t>
+          <t>BUS-GNDOUT-B pin 1</t>
         </is>
       </c>
     </row>
@@ -4381,7 +4515,7 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>splice sp_chassis (SP-GND-CHASSIS: ECU power ground)</t>
+          <t>splice sp_gnd_ecu (SP-GND-ECU: ECU power ground)</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4713,7 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>splice sp_chassis (SP-GND-CHASSIS: ECU power ground)</t>
+          <t>splice sp_gnd_ecu (SP-GND-ECU: ECU power ground)</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4724,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4670,7 +4804,7 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>splice sp_gndout_b (SP-GNDOUT-B)</t>
+          <t>BUS-GNDOUT-B pin 2</t>
         </is>
       </c>
     </row>
@@ -4681,7 +4815,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4741,7 +4875,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>splice sp_5v_b (SP-5V-B)</t>
+          <t>BUS-5V pin 11</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4895,7 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>splice sp_gndout_b (SP-GNDOUT-B)</t>
+          <t>BUS-GNDOUT-B pin 3</t>
         </is>
       </c>
     </row>
@@ -4842,4 +4976,474 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BUS-5V (bus_5v_p)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Pin</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Wire</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Other end</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>w67</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>+5 V from ECU A32</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>ECU-A pin A32</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>w_rail_sp_5v_c</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>+5 V throttle sensor</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>BULKHEAD pin 41</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>w_5v_a_c39</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>+5 V MAP sensor</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>BULKHEAD pin 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>w_5v_a_c40</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>+5 V turbo speed</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>BULKHEAD pin 52</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>w_5v_brail_c45</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>+5 V oil pressure</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>BULKHEAD pin 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>w_5v_brail_c46</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>+5 V fuel pressure</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>BULKHEAD pin 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>w_5v_brail_c47</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>+5 V coolant press</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>BULKHEAD pin 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>w_aps_vc1</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>+5 V pedal sensor 1</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>PEDAL pin 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>w210</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>+5 V pedal sensor 2</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>PEDAL pin 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>cab_fspur_5v</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>+5 V front VRC</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>FRONT WS INLINE pin 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>cab_rspur_5v</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>+5 V rear VRC</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>IX-WS-R inline to rear VRC (dash above ECU) pin 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>w_5v_bus_link</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>+5 V to BUS-5V-2</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>BUS-5V-2 pin 1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:D14"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BUS-5V-2 (bus_5v2_p)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Pin</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Wire</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Other end</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>w_5v_bus_link</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>+5 V from BUS-5V</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>BUS-5V pin 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>w_cru_5v_ac</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>+5 V cruise ladder</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>resistor r_cruise on CSB3 pin 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>w_evap_5v</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>+5 V evap pull-up</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>2.2k evap thermistor pull-up to +5V pin 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>w44</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>+5 V fuel lvl pullup</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>470R fuel level pull-up to +5V pin 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr"/>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr"/>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:D10"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>